--- a/studySpecific/ENSEMBLE/詳細設計書_CombineProcess.xlsx
+++ b/studySpecific/ENSEMBLE/詳細設計書_CombineProcess.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local\iTMS\SDTM_ENSEMBLE\studySpecific\ENSEMBLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B89DD9-FCCB-4080-BD42-920878FDC7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E31636-6E90-4EE9-BD6D-9365B97BC1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="727" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1937,9 +1937,6 @@
     <t>e449ccc</t>
   </si>
   <si>
-    <t>WIP</t>
-  </si>
-  <si>
     <t>張　泊江（Group A）</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -2019,6 +2016,10 @@
   </si>
   <si>
     <t>1.3</t>
+  </si>
+  <si>
+    <t>96985d9</t>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -3085,7 +3086,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -4388,10 +4389,10 @@
         <v>203</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E10" s="30" t="s">
         <v>204</v>
@@ -4428,22 +4429,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" s="30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C12" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="E12" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="F12" s="30" t="s">
         <v>267</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>268</v>
       </c>
       <c r="G12" s="30" t="s">
         <v>180</v>
@@ -4451,22 +4452,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="C13" s="33" t="s">
         <v>270</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="D13" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="E13" s="33" t="s">
         <v>272</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>273</v>
-      </c>
       <c r="F13" s="38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G13" s="33" t="s">
         <v>180</v>
@@ -4636,30 +4637,30 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="C13" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="D13" s="30" t="s">
         <v>259</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="B14" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="C14" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="D14" s="30" t="s">
         <v>263</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +4715,7 @@
         <v>244</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>245</v>
@@ -4731,7 +4732,7 @@
         <v>246</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>247</v>
@@ -4739,7 +4740,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="36" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B6" s="34">
         <v>46066</v>
@@ -4748,7 +4749,7 @@
         <v>248</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>249</v>
@@ -4765,7 +4766,7 @@
         <v>250</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E7" s="30" t="s">
         <v>251</v>
@@ -4782,7 +4783,7 @@
         <v>252</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>253</v>
@@ -4790,19 +4791,19 @@
     </row>
     <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A9" s="37" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B9" s="34">
         <v>46073</v>
       </c>
       <c r="C9" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>279</v>
-      </c>
       <c r="E9" s="33" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
